--- a/data/sub_fields.xlsx
+++ b/data/sub_fields.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,32 +878,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DCGL-1787857981370-6SA86CR2</t>
+          <t>DCGL-1788288248147-8AQ6FHDZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DG38000</t>
+          <t>DG08000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DG38001</t>
+          <t>DG08001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.123537, -12.527279], [34.123539, -12.527279], [34.123541, -12.527278], [34.123543, -12.527278], [34.123544, -12.527277], [34.123544, -12.527276], [34.123549, -12.527275], [34.123557, -12.527275], [34.123558, -12.527275], [34.123563, -12.527277], [34.123564, -12.527278], [34.123567, -12.527282], [34.123568, -12.527283], [34.12357, -12.527288], [34.123571, -12.527293], [34.123571, -12.527297], [34.123569, -12.527301], [34.123568, -12.527302], [34.123566, -12.527304], [34.123563, -12.527307], [34.123562, -12.527308], [34.12356, -12.527308], [34.123557, -12.527311], [34.123553, -12.527313], [34.12355, -12.527314], [34.123547, -12.527314], [34.123544, -12.527314], [34.123541, -12.527315], [34.123539, -12.527313], [34.123536, -12.527312], [34.123535, -12.52731], [34.123535, -12.527309], [34.123535, -12.52731], [34.123536, -12.527309], [34.123536, -12.527309], [34.123535, -12.527309], [34.123534, -12.527308], [34.123534, -12.527308], [34.123534, -12.527308], [34.123534, -12.527308], [34.123537, -12.527279]]]}}</t>
+          <t>{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.123438, -12.5273], [34.123438, -12.527299], [34.123437, -12.527298], [34.123438, -12.527298], [34.123438, -12.527298], [34.123439, -12.527297], [34.123438, -12.527298], [34.12344, -12.527295], [34.12344, -12.527295], [34.12344, -12.527295], [34.123442, -12.527292], [34.123444, -12.527288], [34.123446, -12.527286], [34.123446, -12.527286], [34.123448, -12.527284], [34.12345, -12.527284], [34.123451, -12.527286], [34.123451, -12.527286], [34.123458, -12.52729], [34.123459, -12.52729], [34.123466, -12.527295], [34.123467, -12.527295], [34.123473, -12.527298], [34.123478, -12.527301], [34.123478, -12.527302], [34.123483, -12.527306], [34.123484, -12.527311], [34.123484, -12.527312], [34.123486, -12.527315], [34.123485, -12.527316], [34.123487, -12.527319], [34.123489, -12.527321], [34.123488, -12.527321], [34.123489, -12.527323], [34.123489, -12.527323], [34.12349, -12.527324], [34.123489, -12.527324], [34.123489, -12.527326], [34.123488, -12.527326], [34.123485, -12.527327], [34.123484, -12.527327], [34.12348, -12.52733], [34.123478, -12.52733], [34.123476, -12.52733], [34.123473, -12.527333], [34.123472, -12.527333], [34.123469, -12.527335], [34.123467, -12.527334], [34.123467, -12.527335], [34.123465, -12.527334], [34.123466, -12.527336], [34.123465, -12.527335], [34.123465, -12.527335], [34.123465, -12.527339], [34.123465, -12.527339], [34.123438, -12.5273]]]}}</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-27 21:14</t>
+          <t>2026-09-01 20:44</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -915,35 +915,109 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DCGL-1787858518195-AL94HKBJ</t>
+          <t>DCGL-1788288964949-30Z41WTR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DG09000A</t>
+          <t>DG39000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DG090001</t>
+          <t>DG39001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.123507, -12.527199], [34.123506, -12.527202], [34.123505, -12.527205], [34.123504, -12.527206], [34.123504, -12.527208], [34.123504, -12.527209], [34.123505, -12.527209], [34.123505, -12.527209], [34.123505, -12.52721], [34.123504, -12.527211], [34.123504, -12.527211], [34.123504, -12.527214], [34.123503, -12.527215], [34.123503, -12.527218], [34.123502, -12.52722], [34.123502, -12.527222], [34.123503, -12.527224], [34.123506, -12.527227], [34.123506, -12.527227], [34.12351, -12.527229], [34.123517, -12.52723], [34.123519, -12.527231], [34.123523, -12.527231], [34.123525, -12.527232], [34.123527, -12.527232], [34.12353, -12.527232], [34.123536, -12.527234], [34.123538, -12.527235], [34.123542, -12.527238], [34.123544, -12.52724], [34.123546, -12.527243], [34.123547, -12.527244], [34.12355, -12.527251], [34.123551, -12.527256], [34.123551, -12.527257], [34.12355, -12.527257], [34.12355, -12.527259], [34.123549, -12.52726], [34.123547, -12.527263], [34.123544, -12.527263], [34.123535, -12.527268], [34.123532, -12.527269], [34.123508, -12.527281], [34.123497, -12.527284], [34.123489, -12.527286], [34.123488, -12.527287], [34.123484, -12.527285], [34.123482, -12.527285], [34.123481, -12.527285], [34.123479, -12.527284], [34.123478, -12.527284], [34.123475, -12.527287], [34.123475, -12.527287], [34.123507, -12.527199]]]}}</t>
+          <t>{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.123449, -12.527287], [34.123451, -12.527288], [34.123452, -12.527288], [34.123453, -12.527287], [34.123454, -12.527288], [34.123454, -12.527288], [34.123455, -12.527287], [34.123458, -12.527286], [34.123459, -12.527287], [34.123462, -12.527287], [34.123463, -12.527288], [34.123466, -12.52729], [34.123466, -12.52729], [34.123467, -12.527291], [34.12347, -12.527293], [34.123471, -12.527293], [34.123473, -12.527295], [34.123474, -12.527294], [34.123476, -12.527295], [34.123479, -12.527294], [34.12348, -12.527295], [34.123484, -12.527297], [34.123487, -12.5273], [34.123487, -12.527301], [34.123489, -12.527303], [34.12349, -12.527305], [34.12349, -12.527307], [34.123489, -12.527307], [34.123488, -12.527307], [34.123488, -12.527308], [34.123488, -12.52731], [34.123488, -12.52731], [34.123487, -12.527309], [34.123486, -12.527311], [34.123486, -12.52731], [34.123485, -12.52731], [34.123481, -12.527311], [34.123473, -12.527318], [34.123472, -12.527318], [34.123471, -12.527317], [34.123466, -12.52732], [34.123465, -12.527319], [34.123456, -12.527324], [34.123456, -12.527323], [34.123456, -12.527323], [34.123449, -12.527287]]]}}</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-27 21:28</t>
+          <t>2026-09-01 20:57</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DCGL-1788326820513-XS3WQD1O</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DG10000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DG10001</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.123705, -12.518346], [34.123704, -12.518344], [34.123703, -12.518342], [34.123703, -12.518342], [34.123701, -12.518341], [34.1237, -12.51834], [34.123698, -12.51834], [34.123696, -12.518339], [34.123696, -12.518339], [34.123694, -12.518338], [34.12369, -12.518337], [34.12369, -12.518336], [34.123685, -12.518336], [34.123685, -12.518335], [34.123682, -12.518336], [34.123681, -12.518336], [34.12368, -12.518336], [34.123678, -12.518336], [34.123675, -12.518336], [34.123674, -12.518336], [34.12367, -12.518338], [34.12367, -12.518338], [34.123668, -12.51834], [34.123668, -12.518341], [34.123666, -12.518344], [34.123668, -12.518347], [34.123669, -12.518346], [34.12367, -12.518347], [34.123674, -12.518348], [34.123677, -12.51835], [34.12368, -12.518349], [34.12368, -12.518348], [34.123681, -12.518347], [34.12368, -12.518344], [34.123681, -12.51834], [34.123683, -12.51834], [34.123681, -12.518338], [34.123682, -12.518337], [34.123682, -12.518337], [34.123705, -12.518346]]]}}</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-02 07:27</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DCGL-1788327909295-FXM1358A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DG13000A</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DG130001</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.123659, -12.518343], [34.123652, -12.518337], [34.123652, -12.518336], [34.123649, -12.518322], [34.12365, -12.518321], [34.123646, -12.518309], [34.123647, -12.518306], [34.123644, -12.518292], [34.123641, -12.518284], [34.123634, -12.518283], [34.123625, -12.518285], [34.123621, -12.518288], [34.12362, -12.518292], [34.123618, -12.518298], [34.12362, -12.5183], [34.123626, -12.518303], [34.123623, -12.518298], [34.12363, -12.518295], [34.123627, -12.518291], [34.123629, -12.518289], [34.123633, -12.518287], [34.123634, -12.518286], [34.123634, -12.518286], [34.123659, -12.518343]]]}}</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-09-02 07:45</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>psibale</t>
         </is>

--- a/data/sub_fields.xlsx
+++ b/data/sub_fields.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,32 +878,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DCGL-1788288248147-8AQ6FHDZ</t>
+          <t>DCGL-1788519061650-NGMZYX0M</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DG08000</t>
+          <t>DG09000A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DG08001</t>
+          <t>DG090001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.123438, -12.5273], [34.123438, -12.527299], [34.123437, -12.527298], [34.123438, -12.527298], [34.123438, -12.527298], [34.123439, -12.527297], [34.123438, -12.527298], [34.12344, -12.527295], [34.12344, -12.527295], [34.12344, -12.527295], [34.123442, -12.527292], [34.123444, -12.527288], [34.123446, -12.527286], [34.123446, -12.527286], [34.123448, -12.527284], [34.12345, -12.527284], [34.123451, -12.527286], [34.123451, -12.527286], [34.123458, -12.52729], [34.123459, -12.52729], [34.123466, -12.527295], [34.123467, -12.527295], [34.123473, -12.527298], [34.123478, -12.527301], [34.123478, -12.527302], [34.123483, -12.527306], [34.123484, -12.527311], [34.123484, -12.527312], [34.123486, -12.527315], [34.123485, -12.527316], [34.123487, -12.527319], [34.123489, -12.527321], [34.123488, -12.527321], [34.123489, -12.527323], [34.123489, -12.527323], [34.12349, -12.527324], [34.123489, -12.527324], [34.123489, -12.527326], [34.123488, -12.527326], [34.123485, -12.527327], [34.123484, -12.527327], [34.12348, -12.52733], [34.123478, -12.52733], [34.123476, -12.52733], [34.123473, -12.527333], [34.123472, -12.527333], [34.123469, -12.527335], [34.123467, -12.527334], [34.123467, -12.527335], [34.123465, -12.527334], [34.123466, -12.527336], [34.123465, -12.527335], [34.123465, -12.527335], [34.123465, -12.527339], [34.123465, -12.527339], [34.123438, -12.5273]]]}}</t>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 8, "area_m2": 9.93603515625, "area_ha": 0.000993603515625, "perimeter_m": 17.405575839726794, "survey_distance_m": 9.39056175339478, "best_accuracy_m": 3, "worst_accuracy_m": 3.5350000858306885, "average_accuracy_m": 3.2848750352859497, "survey_started": "2026-09-04T10:50:43.062Z", "survey_completed": "2026-09-04T10:51:01.629Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123756, -12.518411], [34.123753, -12.518391], [34.12375, -12.518381], [34.123738, -12.518375], [34.123729, -12.518373], [34.123719, -12.518373], [34.123708, -12.518371], [34.123697, -12.518367], [34.123756, -12.518411]]]}}</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-01 20:44</t>
+          <t>2026-09-04 12:51</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DCGL-1788288964949-30Z41WTR</t>
+          <t>DCGL-1788545953467-VHILGXRL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -931,16 +931,16 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.123449, -12.527287], [34.123451, -12.527288], [34.123452, -12.527288], [34.123453, -12.527287], [34.123454, -12.527288], [34.123454, -12.527288], [34.123455, -12.527287], [34.123458, -12.527286], [34.123459, -12.527287], [34.123462, -12.527287], [34.123463, -12.527288], [34.123466, -12.52729], [34.123466, -12.52729], [34.123467, -12.527291], [34.12347, -12.527293], [34.123471, -12.527293], [34.123473, -12.527295], [34.123474, -12.527294], [34.123476, -12.527295], [34.123479, -12.527294], [34.12348, -12.527295], [34.123484, -12.527297], [34.123487, -12.5273], [34.123487, -12.527301], [34.123489, -12.527303], [34.12349, -12.527305], [34.12349, -12.527307], [34.123489, -12.527307], [34.123488, -12.527307], [34.123488, -12.527308], [34.123488, -12.52731], [34.123488, -12.52731], [34.123487, -12.527309], [34.123486, -12.527311], [34.123486, -12.52731], [34.123485, -12.52731], [34.123481, -12.527311], [34.123473, -12.527318], [34.123472, -12.527318], [34.123471, -12.527317], [34.123466, -12.52732], [34.123465, -12.527319], [34.123456, -12.527324], [34.123456, -12.527323], [34.123456, -12.527323], [34.123449, -12.527287]]]}}</t>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 3, "area_m2": 0.1484375, "area_ha": 1.484375e-05, "perimeter_m": 4.72802615989826, "survey_distance_m": 2.3701559035970146, "best_accuracy_m": 3, "worst_accuracy_m": 3.9230000972747803, "average_accuracy_m": 3.5923333962758384, "survey_started": "2026-09-04T18:18:49.176Z", "survey_completed": "2026-09-04T18:19:13.451Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123495, -12.527181], [34.123501, -12.527188], [34.123506, -12.527199], [34.123495, -12.527181]]]}}</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-01 20:57</t>
+          <t>2026-09-04 20:19</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -952,17 +952,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DCGL-1788326820513-XS3WQD1O</t>
+          <t>DCGL-1788546763814-5TAOTKXW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DG10000</t>
+          <t>DG06000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DG10001</t>
+          <t>DG06001</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -972,54 +972,387 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.123705, -12.518346], [34.123704, -12.518344], [34.123703, -12.518342], [34.123703, -12.518342], [34.123701, -12.518341], [34.1237, -12.51834], [34.123698, -12.51834], [34.123696, -12.518339], [34.123696, -12.518339], [34.123694, -12.518338], [34.12369, -12.518337], [34.12369, -12.518336], [34.123685, -12.518336], [34.123685, -12.518335], [34.123682, -12.518336], [34.123681, -12.518336], [34.12368, -12.518336], [34.123678, -12.518336], [34.123675, -12.518336], [34.123674, -12.518336], [34.12367, -12.518338], [34.12367, -12.518338], [34.123668, -12.51834], [34.123668, -12.518341], [34.123666, -12.518344], [34.123668, -12.518347], [34.123669, -12.518346], [34.12367, -12.518347], [34.123674, -12.518348], [34.123677, -12.51835], [34.12368, -12.518349], [34.12368, -12.518348], [34.123681, -12.518347], [34.12368, -12.518344], [34.123681, -12.51834], [34.123683, -12.51834], [34.123681, -12.518338], [34.123682, -12.518337], [34.123682, -12.518337], [34.123705, -12.518346]]]}}</t>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 3, "area_m2": 0.03271484375, "area_ha": 3.271484375e-06, "perimeter_m": 4.871891843271445, "survey_distance_m": 2.436223142341008, "best_accuracy_m": 3.0950000286102295, "worst_accuracy_m": 3.7799999713897705, "average_accuracy_m": 3.3399999936421714, "survey_started": "2026-09-04T18:32:22.064Z", "survey_completed": "2026-09-04T18:32:43.796Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.12349, -12.527288], [34.123479, -12.527287], [34.123468, -12.527285], [34.12349, -12.527288]]]}}</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-02 07:27</t>
+          <t>2026-09-04 20:32</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>psibale</t>
+          <t>cjanuary</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DCGL-1788327909295-FXM1358A</t>
+          <t>DCGL-1788547558536-ZA80EPWJ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DG13000A</t>
+          <t>DG08000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DG130001</t>
+          <t>DG08001</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 11, "area_m2": 84.63232421875, "area_ha": 0.008463232421875, "perimeter_m": 65.35386619427048, "survey_distance_m": 46.42439131213428, "best_accuracy_m": 3, "worst_accuracy_m": 15.880000114440918, "average_accuracy_m": 7.903909054669467, "survey_started": "2026-09-04T18:45:28.558Z", "survey_completed": "2026-09-04T18:45:58.516Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.12354, -12.527261], [34.123672, -12.527284], [34.123565, -12.527315], [34.123576, -12.52736], [34.123595, -12.527393], [34.123592, -12.527422], [34.123587, -12.527443], [34.123592, -12.527451], [34.123586, -12.527441], [34.123575, -12.527433], [34.123566, -12.527429], [34.12354, -12.527261]]]}}</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:46</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>cjanuary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DCGL-1788548011317-U4PGG9HU</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DG15000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DG15001</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
         <v>0</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {}, "geometry": {"type": "Polygon", "coordinates": [[[34.123659, -12.518343], [34.123652, -12.518337], [34.123652, -12.518336], [34.123649, -12.518322], [34.12365, -12.518321], [34.123646, -12.518309], [34.123647, -12.518306], [34.123644, -12.518292], [34.123641, -12.518284], [34.123634, -12.518283], [34.123625, -12.518285], [34.123621, -12.518288], [34.12362, -12.518292], [34.123618, -12.518298], [34.12362, -12.5183], [34.123626, -12.518303], [34.123623, -12.518298], [34.12363, -12.518295], [34.123627, -12.518291], [34.123629, -12.518289], [34.123633, -12.518287], [34.123634, -12.518286], [34.123634, -12.518286], [34.123659, -12.518343]]]}}</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-09-02 07:45</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 5, "area_m2": 0.67822265625, "area_ha": 6.7822265625e-05, "perimeter_m": 6.297271707810823, "survey_distance_m": 4.460500109613376, "best_accuracy_m": 3, "worst_accuracy_m": 3.0880000591278076, "average_accuracy_m": 3.0176000118255617, "survey_started": "2026-09-04T18:52:47.468Z", "survey_completed": "2026-09-04T18:53:31.285Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123504, -12.527306], [34.12351, -12.527299], [34.123517, -12.527291], [34.123512, -12.527298], [34.123504, -12.52729], [34.123504, -12.527306]]]}}</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-09-05 09:36</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>cjanuary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DCGL-1788594984287-CDX9WSZD</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DG08000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DG08001</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 28, "area_m2": 64.13671875, "area_ha": 0.006413671875, "perimeter_m": 37.419104598646776, "survey_distance_m": 36.1502179443404, "best_accuracy_m": 3, "worst_accuracy_m": 5.508999824523926, "average_accuracy_m": 3.2834642699786594, "survey_started": "2026-09-05T07:55:41.789Z", "survey_completed": "2026-09-05T07:56:24.274Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123584, -12.518369], [34.123568, -12.518371], [34.123558, -12.518375], [34.123546, -12.518376], [34.123533, -12.51838], [34.123517, -12.518384], [34.123508, -12.518387], [34.123496, -12.518392], [34.123485, -12.518399], [34.123477, -12.518404], [34.123467, -12.51841], [34.123455, -12.518407], [34.123451, -12.518395], [34.12345, -12.51838], [34.123454, -12.518367], [34.123467, -12.51836], [34.123477, -12.518357], [34.123487, -12.518355], [34.123498, -12.518352], [34.12351, -12.518346], [34.123519, -12.51834], [34.123532, -12.518337], [34.123542, -12.518332], [34.123551, -12.51833], [34.123561, -12.518333], [34.123566, -12.518344], [34.123569, -12.518356], [34.123572, -12.518367], [34.123584, -12.518369]]]}}</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-09-05 09:57</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>psibale</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DCGL-1788595189010-DGFSVCQT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DG02000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DG02002</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 30, "area_m2": 93.52783203125, "area_ha": 0.009352783203125, "perimeter_m": 39.8506104983367, "survey_distance_m": 37.10159936326611, "best_accuracy_m": 3, "worst_accuracy_m": 3.0759999752044678, "average_accuracy_m": 3.0097333431243896, "survey_started": "2026-09-05T07:59:01.374Z", "survey_completed": "2026-09-05T07:59:48.991Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123595, -12.518384], [34.123585, -12.518385], [34.123571, -12.518392], [34.123558, -12.518397], [34.123547, -12.518402], [34.123532, -12.518407], [34.123521, -12.518413], [34.123511, -12.518415], [34.1235, -12.518417], [34.12349, -12.518421], [34.123478, -12.518424], [34.123467, -12.518415], [34.123464, -12.518402], [34.123465, -12.51839], [34.123461, -12.518379], [34.123463, -12.51837], [34.123472, -12.518366], [34.123481, -12.518364], [34.123492, -12.518361], [34.123501, -12.518357], [34.123511, -12.518353], [34.123523, -12.518345], [34.123532, -12.51834], [34.123541, -12.518336], [34.123551, -12.51833], [34.12356, -12.518329], [34.123572, -12.51833], [34.123576, -12.518341], [34.123579, -12.518353], [34.123582, -12.518363], [34.123595, -12.518384]]]}}</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:08</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DCGL-1788596388569-7MIWC0E6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DG03000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DG03001</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 3, "area_m2": 0.0400390625, "area_ha": 4.00390625e-06, "perimeter_m": 5.596594863293685, "survey_distance_m": 2.7985783811387597, "best_accuracy_m": 5.197999954223633, "worst_accuracy_m": 7.770999908447266, "average_accuracy_m": 6.52400000890096, "survey_started": "2026-09-05T08:19:37.073Z", "survey_completed": "2026-09-05T08:19:48.547Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123684, -12.518357], [34.123678, -12.518342], [34.123675, -12.518334], [34.123684, -12.518357]]]}}</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-09-05 10:19</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DCGL-1788596511286-S4EOZO7P</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DG03000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DG03001</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 31, "area_m2": 93.18310546875, "area_ha": 0.009318310546875, "perimeter_m": 45.776944693846254, "survey_distance_m": 38.231412634700284, "best_accuracy_m": 3, "worst_accuracy_m": 4.354000091552734, "average_accuracy_m": 3.2143225977497716, "survey_started": "2026-09-05T08:21:00.488Z", "survey_completed": "2026-09-05T08:21:51.265Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123612, -12.518346], [34.123603, -12.518351], [34.123593, -12.518358], [34.123573, -12.518372], [34.123567, -12.518379], [34.123556, -12.518386], [34.123542, -12.518391], [34.123533, -12.518396], [34.123523, -12.5184], [34.12351, -12.518403], [34.123496, -12.518405], [34.123487, -12.518409], [34.123478, -12.51841], [34.123467, -12.518411], [34.123454, -12.518409], [34.123449, -12.5184], [34.123444, -12.51839], [34.123442, -12.51838], [34.123443, -12.518369], [34.123453, -12.518362], [34.123464, -12.51836], [34.123477, -12.518357], [34.123487, -12.518355], [34.123494, -12.518348], [34.123499, -12.518338], [34.123506, -12.518328], [34.123514, -12.518324], [34.123526, -12.518323], [34.123532, -12.518333], [34.123537, -12.518341], [34.123542, -12.518348], [34.123612, -12.518346]]]}}</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-09-07 10:21</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>cjanuary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DCGL-1788769597730-NI5VWJ2U</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DG10000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DG10001</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 26, "area_m2": 84.33154296875, "area_ha": 0.008433154296875, "perimeter_m": 38.465750534152676, "survey_distance_m": 31.35098253482801, "best_accuracy_m": 3, "worst_accuracy_m": 3.2260000705718994, "average_accuracy_m": 3.0585000056486864, "survey_started": "2026-09-07T08:25:52.739Z", "survey_completed": "2026-09-07T08:26:37.701Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123583, -12.518376], [34.123575, -12.518382], [34.123562, -12.518386], [34.123552, -12.518391], [34.123542, -12.518396], [34.123532, -12.5184], [34.12352, -12.518404], [34.123509, -12.518408], [34.123499, -12.518411], [34.123488, -12.518414], [34.123478, -12.518418], [34.123467, -12.518416], [34.123464, -12.518406], [34.123462, -12.518394], [34.123458, -12.518381], [34.123458, -12.518371], [34.123467, -12.518364], [34.123479, -12.518362], [34.123492, -12.518359], [34.123501, -12.518356], [34.123509, -12.518351], [34.123518, -12.518345], [34.123531, -12.518336], [34.123538, -12.518327], [34.123548, -12.518323], [34.123557, -12.518317], [34.123583, -12.518376]]]}}</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-09-07 10:27</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>hlungu</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DCGL-1788772310074-YX23CV83</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DG12000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DG12003</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 3, "area_m2": 0.75830078125, "area_ha": 7.5830078125e-05, "perimeter_m": 7.365526631369606, "survey_distance_m": 3.7263327691018224, "best_accuracy_m": 4.631999969482422, "worst_accuracy_m": 8.307000160217285, "average_accuracy_m": 6.703666687011719, "survey_started": "2026-09-07T09:11:42.975Z", "survey_completed": "2026-09-07T09:11:50.056Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123627, -12.518163], [34.123639, -12.518172], [34.123647, -12.518189], [34.123627, -12.518163]]]}}</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-09-07 11:11</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>hlungu</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DCGL-1788772434957-T89FXIVD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DG16000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DG16001</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 24, "area_m2": 111.58837890625, "area_ha": 0.011158837890625, "perimeter_m": 44.81649845506116, "survey_distance_m": 42.334319681904084, "best_accuracy_m": 3, "worst_accuracy_m": 21.509000778198242, "average_accuracy_m": 4.291208376487096, "survey_started": "2026-09-07T09:13:10.915Z", "survey_completed": "2026-09-07T09:13:54.941Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123578, -12.518391], [34.123579, -12.51838], [34.123572, -12.518362], [34.123564, -12.518345], [34.123557, -12.518334], [34.123549, -12.518323], [34.123537, -12.518315], [34.123527, -12.518317], [34.123519, -12.51832], [34.123506, -12.518325], [34.123491, -12.518329], [34.123481, -12.518334], [34.12347, -12.51834], [34.123462, -12.518349], [34.123459, -12.518362], [34.123453, -12.518369], [34.123445, -12.518376], [34.123447, -12.518386], [34.123454, -12.518399], [34.123462, -12.518408], [34.123475, -12.518414], [34.123485, -12.518413], [34.123534, -12.518392], [34.123595, -12.518406], [34.123578, -12.518391]]]}}</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-09-07 11:18</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>hlungu</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DCGL-1788776173911-EIWKVP4S</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DG09000B</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DG090001</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 5, "area_m2": 2.10546875, "area_ha": 0.000210546875, "perimeter_m": 8.668048781028403, "survey_distance_m": 4.536196323835277, "best_accuracy_m": 3, "worst_accuracy_m": 3.2690000534057617, "average_accuracy_m": 3.088600015640259, "survey_started": "2026-09-07T10:15:55.014Z", "survey_completed": "2026-09-07T10:16:13.890Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123695, -12.518372], [34.123684, -12.51837], [34.123673, -12.518373], [34.123664, -12.518376], [34.123659, -12.518384], [34.123695, -12.518372]]]}}</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:16</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>hlungu</t>
         </is>
       </c>
     </row>

--- a/data/sub_fields.xlsx
+++ b/data/sub_fields.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,44 +878,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DCGL-1788519061650-NGMZYX0M</t>
+          <t>DCGL-1789550186416-FAA8LNWK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DG09000A</t>
+          <t>DG39000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DG090001</t>
+          <t>DG39001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 8, "area_m2": 9.93603515625, "area_ha": 0.000993603515625, "perimeter_m": 17.405575839726794, "survey_distance_m": 9.39056175339478, "best_accuracy_m": 3, "worst_accuracy_m": 3.5350000858306885, "average_accuracy_m": 3.2848750352859497, "survey_started": "2026-09-04T10:50:43.062Z", "survey_completed": "2026-09-04T10:51:01.629Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123756, -12.518411], [34.123753, -12.518391], [34.12375, -12.518381], [34.123738, -12.518375], [34.123729, -12.518373], [34.123719, -12.518373], [34.123708, -12.518371], [34.123697, -12.518367], [34.123756, -12.518411]]]}}</t>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 5, "area_m2": 4.98388671875, "area_ha": 0.000498388671875, "perimeter_m": 12.52270950217982, "survey_distance_m": 7.098790928235161, "best_accuracy_m": 3.0409998893737793, "worst_accuracy_m": 5.436999797821045, "average_accuracy_m": 3.6323999881744387, "survey_started": "2026-09-16T09:16:11.870Z", "survey_completed": "2026-09-16T09:16:26.398Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123709, -12.518406], [34.123687, -12.518387], [34.123675, -12.518376], [34.123674, -12.518367], [34.123684, -12.518364], [34.123709, -12.518406]]]}}</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-04 12:51</t>
+          <t>2026-09-16 11:16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>psibale</t>
+          <t>cjanuary</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DCGL-1788545953467-VHILGXRL</t>
+          <t>DCGL-1789550303338-LMTZHA7F</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -935,424 +935,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 3, "area_m2": 0.1484375, "area_ha": 1.484375e-05, "perimeter_m": 4.72802615989826, "survey_distance_m": 2.3701559035970146, "best_accuracy_m": 3, "worst_accuracy_m": 3.9230000972747803, "average_accuracy_m": 3.5923333962758384, "survey_started": "2026-09-04T18:18:49.176Z", "survey_completed": "2026-09-04T18:19:13.451Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123495, -12.527181], [34.123501, -12.527188], [34.123506, -12.527199], [34.123495, -12.527181]]]}}</t>
+          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 6, "area_m2": 2.78369140625, "area_ha": 0.000278369140625, "perimeter_m": 7.488150033121251, "survey_distance_m": 6.618159513019729, "best_accuracy_m": 3, "worst_accuracy_m": 3.319999933242798, "average_accuracy_m": 3.1203333139419556, "survey_started": "2026-09-16T09:18:00.355Z", "survey_completed": "2026-09-16T09:18:23.319Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123682, -12.518324], [34.12368, -12.518335], [34.123674, -12.518346], [34.123668, -12.518333], [34.123672, -12.518323], [34.123682, -12.518316], [34.123682, -12.518324]]]}}</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-04 20:19</t>
+          <t>2026-09-16 11:34</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>psibale</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>DCGL-1788546763814-5TAOTKXW</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DG06000</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DG06001</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 3, "area_m2": 0.03271484375, "area_ha": 3.271484375e-06, "perimeter_m": 4.871891843271445, "survey_distance_m": 2.436223142341008, "best_accuracy_m": 3.0950000286102295, "worst_accuracy_m": 3.7799999713897705, "average_accuracy_m": 3.3399999936421714, "survey_started": "2026-09-04T18:32:22.064Z", "survey_completed": "2026-09-04T18:32:43.796Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.12349, -12.527288], [34.123479, -12.527287], [34.123468, -12.527285], [34.12349, -12.527288]]]}}</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-09-04 20:32</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
           <t>cjanuary</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>DCGL-1788547558536-ZA80EPWJ</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DG08000</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DG08001</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 11, "area_m2": 84.63232421875, "area_ha": 0.008463232421875, "perimeter_m": 65.35386619427048, "survey_distance_m": 46.42439131213428, "best_accuracy_m": 3, "worst_accuracy_m": 15.880000114440918, "average_accuracy_m": 7.903909054669467, "survey_started": "2026-09-04T18:45:28.558Z", "survey_completed": "2026-09-04T18:45:58.516Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.12354, -12.527261], [34.123672, -12.527284], [34.123565, -12.527315], [34.123576, -12.52736], [34.123595, -12.527393], [34.123592, -12.527422], [34.123587, -12.527443], [34.123592, -12.527451], [34.123586, -12.527441], [34.123575, -12.527433], [34.123566, -12.527429], [34.12354, -12.527261]]]}}</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-09-04 20:46</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>cjanuary</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DCGL-1788548011317-U4PGG9HU</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>DG15000</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DG15001</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 5, "area_m2": 0.67822265625, "area_ha": 6.7822265625e-05, "perimeter_m": 6.297271707810823, "survey_distance_m": 4.460500109613376, "best_accuracy_m": 3, "worst_accuracy_m": 3.0880000591278076, "average_accuracy_m": 3.0176000118255617, "survey_started": "2026-09-04T18:52:47.468Z", "survey_completed": "2026-09-04T18:53:31.285Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123504, -12.527306], [34.12351, -12.527299], [34.123517, -12.527291], [34.123512, -12.527298], [34.123504, -12.52729], [34.123504, -12.527306]]]}}</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-09-05 09:36</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>cjanuary</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DCGL-1788594984287-CDX9WSZD</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>DG08000</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DG08001</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 28, "area_m2": 64.13671875, "area_ha": 0.006413671875, "perimeter_m": 37.419104598646776, "survey_distance_m": 36.1502179443404, "best_accuracy_m": 3, "worst_accuracy_m": 5.508999824523926, "average_accuracy_m": 3.2834642699786594, "survey_started": "2026-09-05T07:55:41.789Z", "survey_completed": "2026-09-05T07:56:24.274Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123584, -12.518369], [34.123568, -12.518371], [34.123558, -12.518375], [34.123546, -12.518376], [34.123533, -12.51838], [34.123517, -12.518384], [34.123508, -12.518387], [34.123496, -12.518392], [34.123485, -12.518399], [34.123477, -12.518404], [34.123467, -12.51841], [34.123455, -12.518407], [34.123451, -12.518395], [34.12345, -12.51838], [34.123454, -12.518367], [34.123467, -12.51836], [34.123477, -12.518357], [34.123487, -12.518355], [34.123498, -12.518352], [34.12351, -12.518346], [34.123519, -12.51834], [34.123532, -12.518337], [34.123542, -12.518332], [34.123551, -12.51833], [34.123561, -12.518333], [34.123566, -12.518344], [34.123569, -12.518356], [34.123572, -12.518367], [34.123584, -12.518369]]]}}</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-09-05 09:57</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>psibale</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DCGL-1788595189010-DGFSVCQT</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>DG02000</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DG02002</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 30, "area_m2": 93.52783203125, "area_ha": 0.009352783203125, "perimeter_m": 39.8506104983367, "survey_distance_m": 37.10159936326611, "best_accuracy_m": 3, "worst_accuracy_m": 3.0759999752044678, "average_accuracy_m": 3.0097333431243896, "survey_started": "2026-09-05T07:59:01.374Z", "survey_completed": "2026-09-05T07:59:48.991Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123595, -12.518384], [34.123585, -12.518385], [34.123571, -12.518392], [34.123558, -12.518397], [34.123547, -12.518402], [34.123532, -12.518407], [34.123521, -12.518413], [34.123511, -12.518415], [34.1235, -12.518417], [34.12349, -12.518421], [34.123478, -12.518424], [34.123467, -12.518415], [34.123464, -12.518402], [34.123465, -12.51839], [34.123461, -12.518379], [34.123463, -12.51837], [34.123472, -12.518366], [34.123481, -12.518364], [34.123492, -12.518361], [34.123501, -12.518357], [34.123511, -12.518353], [34.123523, -12.518345], [34.123532, -12.51834], [34.123541, -12.518336], [34.123551, -12.51833], [34.12356, -12.518329], [34.123572, -12.51833], [34.123576, -12.518341], [34.123579, -12.518353], [34.123582, -12.518363], [34.123595, -12.518384]]]}}</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-09-05 10:08</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>psibale</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>DCGL-1788596388569-7MIWC0E6</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>DG03000</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DG03001</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 3, "area_m2": 0.0400390625, "area_ha": 4.00390625e-06, "perimeter_m": 5.596594863293685, "survey_distance_m": 2.7985783811387597, "best_accuracy_m": 5.197999954223633, "worst_accuracy_m": 7.770999908447266, "average_accuracy_m": 6.52400000890096, "survey_started": "2026-09-05T08:19:37.073Z", "survey_completed": "2026-09-05T08:19:48.547Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123684, -12.518357], [34.123678, -12.518342], [34.123675, -12.518334], [34.123684, -12.518357]]]}}</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-09-05 10:19</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>psibale</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>DCGL-1788596511286-S4EOZO7P</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>DG03000</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DG03001</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 31, "area_m2": 93.18310546875, "area_ha": 0.009318310546875, "perimeter_m": 45.776944693846254, "survey_distance_m": 38.231412634700284, "best_accuracy_m": 3, "worst_accuracy_m": 4.354000091552734, "average_accuracy_m": 3.2143225977497716, "survey_started": "2026-09-05T08:21:00.488Z", "survey_completed": "2026-09-05T08:21:51.265Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123612, -12.518346], [34.123603, -12.518351], [34.123593, -12.518358], [34.123573, -12.518372], [34.123567, -12.518379], [34.123556, -12.518386], [34.123542, -12.518391], [34.123533, -12.518396], [34.123523, -12.5184], [34.12351, -12.518403], [34.123496, -12.518405], [34.123487, -12.518409], [34.123478, -12.51841], [34.123467, -12.518411], [34.123454, -12.518409], [34.123449, -12.5184], [34.123444, -12.51839], [34.123442, -12.51838], [34.123443, -12.518369], [34.123453, -12.518362], [34.123464, -12.51836], [34.123477, -12.518357], [34.123487, -12.518355], [34.123494, -12.518348], [34.123499, -12.518338], [34.123506, -12.518328], [34.123514, -12.518324], [34.123526, -12.518323], [34.123532, -12.518333], [34.123537, -12.518341], [34.123542, -12.518348], [34.123612, -12.518346]]]}}</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-09-07 10:21</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>cjanuary</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DCGL-1788769597730-NI5VWJ2U</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>DG10000</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DG10001</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 26, "area_m2": 84.33154296875, "area_ha": 0.008433154296875, "perimeter_m": 38.465750534152676, "survey_distance_m": 31.35098253482801, "best_accuracy_m": 3, "worst_accuracy_m": 3.2260000705718994, "average_accuracy_m": 3.0585000056486864, "survey_started": "2026-09-07T08:25:52.739Z", "survey_completed": "2026-09-07T08:26:37.701Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123583, -12.518376], [34.123575, -12.518382], [34.123562, -12.518386], [34.123552, -12.518391], [34.123542, -12.518396], [34.123532, -12.5184], [34.12352, -12.518404], [34.123509, -12.518408], [34.123499, -12.518411], [34.123488, -12.518414], [34.123478, -12.518418], [34.123467, -12.518416], [34.123464, -12.518406], [34.123462, -12.518394], [34.123458, -12.518381], [34.123458, -12.518371], [34.123467, -12.518364], [34.123479, -12.518362], [34.123492, -12.518359], [34.123501, -12.518356], [34.123509, -12.518351], [34.123518, -12.518345], [34.123531, -12.518336], [34.123538, -12.518327], [34.123548, -12.518323], [34.123557, -12.518317], [34.123583, -12.518376]]]}}</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-09-07 10:27</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>hlungu</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>DCGL-1788772310074-YX23CV83</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>DG12000</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DG12003</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 3, "area_m2": 0.75830078125, "area_ha": 7.5830078125e-05, "perimeter_m": 7.365526631369606, "survey_distance_m": 3.7263327691018224, "best_accuracy_m": 4.631999969482422, "worst_accuracy_m": 8.307000160217285, "average_accuracy_m": 6.703666687011719, "survey_started": "2026-09-07T09:11:42.975Z", "survey_completed": "2026-09-07T09:11:50.056Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123627, -12.518163], [34.123639, -12.518172], [34.123647, -12.518189], [34.123627, -12.518163]]]}}</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-09-07 11:11</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>hlungu</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>DCGL-1788772434957-T89FXIVD</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>DG16000</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DG16001</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 24, "area_m2": 111.58837890625, "area_ha": 0.011158837890625, "perimeter_m": 44.81649845506116, "survey_distance_m": 42.334319681904084, "best_accuracy_m": 3, "worst_accuracy_m": 21.509000778198242, "average_accuracy_m": 4.291208376487096, "survey_started": "2026-09-07T09:13:10.915Z", "survey_completed": "2026-09-07T09:13:54.941Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123578, -12.518391], [34.123579, -12.51838], [34.123572, -12.518362], [34.123564, -12.518345], [34.123557, -12.518334], [34.123549, -12.518323], [34.123537, -12.518315], [34.123527, -12.518317], [34.123519, -12.51832], [34.123506, -12.518325], [34.123491, -12.518329], [34.123481, -12.518334], [34.12347, -12.51834], [34.123462, -12.518349], [34.123459, -12.518362], [34.123453, -12.518369], [34.123445, -12.518376], [34.123447, -12.518386], [34.123454, -12.518399], [34.123462, -12.518408], [34.123475, -12.518414], [34.123485, -12.518413], [34.123534, -12.518392], [34.123595, -12.518406], [34.123578, -12.518391]]]}}</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-09-07 11:18</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>hlungu</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>DCGL-1788776173911-EIWKVP4S</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>DG09000B</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DG090001</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>{"type": "Feature", "properties": {"survey_type": "Field Boundary Survey", "point_count": 5, "area_m2": 2.10546875, "area_ha": 0.000210546875, "perimeter_m": 8.668048781028403, "survey_distance_m": 4.536196323835277, "best_accuracy_m": 3, "worst_accuracy_m": 3.2690000534057617, "average_accuracy_m": 3.088600015640259, "survey_started": "2026-09-07T10:15:55.014Z", "survey_completed": "2026-09-07T10:16:13.890Z"}, "geometry": {"type": "Polygon", "coordinates": [[[34.123695, -12.518372], [34.123684, -12.51837], [34.123673, -12.518373], [34.123664, -12.518376], [34.123659, -12.518384], [34.123695, -12.518372]]]}}</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-09-07 12:16</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>hlungu</t>
         </is>
       </c>
     </row>
